--- a/artfynd/A 30484-2025 artfynd.xlsx
+++ b/artfynd/A 30484-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1034,6 +1034,903 @@
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>128481937</v>
+      </c>
+      <c r="B5" t="n">
+        <v>90987</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>5747</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Läderdoftande fingersvamp</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Ramaria safraniolens</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Christan</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Flät, Upl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>629885</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6720262</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>128482768</v>
+      </c>
+      <c r="B6" t="n">
+        <v>86915</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Flät, Upl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>629958</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6720276</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>128494722</v>
+      </c>
+      <c r="B7" t="n">
+        <v>92754</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>4366</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Hydnellum peckii</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Flät, Upl</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>629919</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6720276</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>128494750</v>
+      </c>
+      <c r="B8" t="n">
+        <v>86915</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Flät, Upl</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>629940</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6720267</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>128494710</v>
+      </c>
+      <c r="B9" t="n">
+        <v>86878</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>3674</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Anisspindling</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Cortinarius odorifer</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Britzelm.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Flät, Upl</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>629987</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6720190</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>128482901</v>
+      </c>
+      <c r="B10" t="n">
+        <v>86892</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>249228</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Barrfagerspindling</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Cortinarius piceae</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Frøslev &amp; al.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Flät, Upl</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>629986</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6720246</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>128482529</v>
+      </c>
+      <c r="B11" t="n">
+        <v>86716</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>3762</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Olivspindling</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Cortinarius venetus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Flät, Upl</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>629954</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6720288</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>128481990</v>
+      </c>
+      <c r="B12" t="n">
+        <v>92770</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>5449</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Svart taggsvamp</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Phellodon niger</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Flät, Upl</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>629885</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6720262</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>128494737</v>
+      </c>
+      <c r="B13" t="n">
+        <v>86716</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>3762</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Olivspindling</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Cortinarius venetus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Flät, Upl</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>629913</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6720256</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 30484-2025 artfynd.xlsx
+++ b/artfynd/A 30484-2025 artfynd.xlsx
@@ -1735,45 +1735,48 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128481990</v>
+        <v>128494737</v>
       </c>
       <c r="B12" t="n">
-        <v>92770</v>
+        <v>86716</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5449</v>
+        <v>3762</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Flät, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>629885</v>
+        <v>629913</v>
       </c>
       <c r="R12" t="n">
-        <v>6720262</v>
+        <v>6720256</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1814,6 +1817,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1832,48 +1836,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128494737</v>
+        <v>128481990</v>
       </c>
       <c r="B13" t="n">
-        <v>86716</v>
+        <v>92770</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>3762</v>
+        <v>5449</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Flät, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>629913</v>
+        <v>629885</v>
       </c>
       <c r="R13" t="n">
-        <v>6720256</v>
+        <v>6720262</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1914,7 +1915,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 30484-2025 artfynd.xlsx
+++ b/artfynd/A 30484-2025 artfynd.xlsx
@@ -1735,48 +1735,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128494737</v>
+        <v>128481990</v>
       </c>
       <c r="B12" t="n">
-        <v>86716</v>
+        <v>92770</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>3762</v>
+        <v>5449</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Flät, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>629913</v>
+        <v>629885</v>
       </c>
       <c r="R12" t="n">
-        <v>6720256</v>
+        <v>6720262</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1817,7 +1814,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1836,45 +1832,48 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128481990</v>
+        <v>128494737</v>
       </c>
       <c r="B13" t="n">
-        <v>92770</v>
+        <v>86716</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5449</v>
+        <v>3762</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Flät, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>629885</v>
+        <v>629913</v>
       </c>
       <c r="R13" t="n">
-        <v>6720262</v>
+        <v>6720256</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1915,6 +1914,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 30484-2025 artfynd.xlsx
+++ b/artfynd/A 30484-2025 artfynd.xlsx
@@ -1036,45 +1036,48 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128481937</v>
+        <v>128482768</v>
       </c>
       <c r="B5" t="n">
-        <v>90987</v>
+        <v>86919</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5747</v>
+        <v>6003295</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Flät, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>629885</v>
+        <v>629958</v>
       </c>
       <c r="R5" t="n">
-        <v>6720262</v>
+        <v>6720276</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1115,6 +1118,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1133,48 +1137,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128482768</v>
+        <v>128481937</v>
       </c>
       <c r="B6" t="n">
-        <v>86915</v>
+        <v>90993</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6003295</v>
+        <v>5747</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Flät, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>629958</v>
+        <v>629885</v>
       </c>
       <c r="R6" t="n">
-        <v>6720276</v>
+        <v>6720262</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1215,7 +1216,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1237,7 +1237,7 @@
         <v>128494722</v>
       </c>
       <c r="B7" t="n">
-        <v>92754</v>
+        <v>92760</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1338,7 +1338,7 @@
         <v>128494750</v>
       </c>
       <c r="B8" t="n">
-        <v>86915</v>
+        <v>86919</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1439,7 +1439,7 @@
         <v>128494710</v>
       </c>
       <c r="B9" t="n">
-        <v>86878</v>
+        <v>86882</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1537,10 +1537,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128482901</v>
+        <v>128482529</v>
       </c>
       <c r="B10" t="n">
-        <v>86892</v>
+        <v>86721</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1548,37 +1548,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>249228</v>
+        <v>3762</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Barrfagerspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cortinarius piceae</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Frøslev &amp; al.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Flät, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>629986</v>
+        <v>629954</v>
       </c>
       <c r="R10" t="n">
-        <v>6720246</v>
+        <v>6720288</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1619,7 +1616,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1638,10 +1634,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128482529</v>
+        <v>128482901</v>
       </c>
       <c r="B11" t="n">
-        <v>86716</v>
+        <v>86896</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1649,34 +1645,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>3762</v>
+        <v>249228</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Barrfagerspindling</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius piceae</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Frøslev &amp; al.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Flät, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>629954</v>
+        <v>629986</v>
       </c>
       <c r="R11" t="n">
-        <v>6720288</v>
+        <v>6720246</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1717,6 +1716,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1735,45 +1735,48 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128481990</v>
+        <v>128494737</v>
       </c>
       <c r="B12" t="n">
-        <v>92770</v>
+        <v>86721</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5449</v>
+        <v>3762</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Flät, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>629885</v>
+        <v>629913</v>
       </c>
       <c r="R12" t="n">
-        <v>6720262</v>
+        <v>6720256</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1814,6 +1817,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1832,48 +1836,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128494737</v>
+        <v>128481990</v>
       </c>
       <c r="B13" t="n">
-        <v>86716</v>
+        <v>92776</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>3762</v>
+        <v>5449</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Flät, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>629913</v>
+        <v>629885</v>
       </c>
       <c r="R13" t="n">
-        <v>6720256</v>
+        <v>6720262</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1914,7 +1915,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 30484-2025 artfynd.xlsx
+++ b/artfynd/A 30484-2025 artfynd.xlsx
@@ -1036,48 +1036,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128482768</v>
+        <v>128481937</v>
       </c>
       <c r="B5" t="n">
-        <v>86919</v>
+        <v>90999</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6003295</v>
+        <v>5747</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Flät, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>629958</v>
+        <v>629885</v>
       </c>
       <c r="R5" t="n">
-        <v>6720276</v>
+        <v>6720262</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1118,7 +1115,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1137,45 +1133,48 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128481937</v>
+        <v>128482768</v>
       </c>
       <c r="B6" t="n">
-        <v>90993</v>
+        <v>86925</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5747</v>
+        <v>6003295</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Flät, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>629885</v>
+        <v>629958</v>
       </c>
       <c r="R6" t="n">
-        <v>6720262</v>
+        <v>6720276</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1216,6 +1215,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1237,7 +1237,7 @@
         <v>128494722</v>
       </c>
       <c r="B7" t="n">
-        <v>92760</v>
+        <v>92766</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1338,7 +1338,7 @@
         <v>128494750</v>
       </c>
       <c r="B8" t="n">
-        <v>86919</v>
+        <v>86925</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1439,7 +1439,7 @@
         <v>128494710</v>
       </c>
       <c r="B9" t="n">
-        <v>86882</v>
+        <v>86888</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1537,10 +1537,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128482529</v>
+        <v>128482901</v>
       </c>
       <c r="B10" t="n">
-        <v>86721</v>
+        <v>86902</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1548,34 +1548,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>3762</v>
+        <v>249228</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Barrfagerspindling</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius piceae</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Frøslev &amp; al.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Flät, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>629954</v>
+        <v>629986</v>
       </c>
       <c r="R10" t="n">
-        <v>6720288</v>
+        <v>6720246</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1616,6 +1619,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1634,10 +1638,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128482901</v>
+        <v>128482529</v>
       </c>
       <c r="B11" t="n">
-        <v>86896</v>
+        <v>86727</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1645,37 +1649,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>249228</v>
+        <v>3762</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Barrfagerspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cortinarius piceae</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Frøslev &amp; al.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Flät, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>629986</v>
+        <v>629954</v>
       </c>
       <c r="R11" t="n">
-        <v>6720246</v>
+        <v>6720288</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1716,7 +1717,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1738,7 +1738,7 @@
         <v>128494737</v>
       </c>
       <c r="B12" t="n">
-        <v>86721</v>
+        <v>86727</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1839,7 +1839,7 @@
         <v>128481990</v>
       </c>
       <c r="B13" t="n">
-        <v>92776</v>
+        <v>92782</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 30484-2025 artfynd.xlsx
+++ b/artfynd/A 30484-2025 artfynd.xlsx
@@ -1039,7 +1039,7 @@
         <v>128481937</v>
       </c>
       <c r="B5" t="n">
-        <v>90999</v>
+        <v>91001</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
         <v>128482768</v>
       </c>
       <c r="B6" t="n">
-        <v>86925</v>
+        <v>86927</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1237,7 +1237,7 @@
         <v>128494722</v>
       </c>
       <c r="B7" t="n">
-        <v>92766</v>
+        <v>92768</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1338,7 +1338,7 @@
         <v>128494750</v>
       </c>
       <c r="B8" t="n">
-        <v>86925</v>
+        <v>86927</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1439,7 +1439,7 @@
         <v>128494710</v>
       </c>
       <c r="B9" t="n">
-        <v>86888</v>
+        <v>86890</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1537,10 +1537,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128482901</v>
+        <v>128482529</v>
       </c>
       <c r="B10" t="n">
-        <v>86902</v>
+        <v>86729</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1548,37 +1548,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>249228</v>
+        <v>3762</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Barrfagerspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cortinarius piceae</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Frøslev &amp; al.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Flät, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>629986</v>
+        <v>629954</v>
       </c>
       <c r="R10" t="n">
-        <v>6720246</v>
+        <v>6720288</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1619,7 +1616,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1638,10 +1634,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128482529</v>
+        <v>128482901</v>
       </c>
       <c r="B11" t="n">
-        <v>86727</v>
+        <v>86904</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1649,34 +1645,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>3762</v>
+        <v>249228</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Barrfagerspindling</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius piceae</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Frøslev &amp; al.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Flät, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>629954</v>
+        <v>629986</v>
       </c>
       <c r="R11" t="n">
-        <v>6720288</v>
+        <v>6720246</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1717,6 +1716,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1738,7 +1738,7 @@
         <v>128494737</v>
       </c>
       <c r="B12" t="n">
-        <v>86727</v>
+        <v>86729</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1839,7 +1839,7 @@
         <v>128481990</v>
       </c>
       <c r="B13" t="n">
-        <v>92782</v>
+        <v>92784</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 30484-2025 artfynd.xlsx
+++ b/artfynd/A 30484-2025 artfynd.xlsx
@@ -1133,32 +1133,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128482768</v>
+        <v>128494722</v>
       </c>
       <c r="B6" t="n">
-        <v>86927</v>
+        <v>92768</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6003295</v>
+        <v>4366</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1171,7 +1171,7 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>629958</v>
+        <v>629919</v>
       </c>
       <c r="R6" t="n">
         <v>6720276</v>
@@ -1234,32 +1234,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128494722</v>
+        <v>128494750</v>
       </c>
       <c r="B7" t="n">
-        <v>92768</v>
+        <v>86927</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4366</v>
+        <v>6003295</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>629919</v>
+        <v>629940</v>
       </c>
       <c r="R7" t="n">
-        <v>6720276</v>
+        <v>6720267</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1335,32 +1335,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128494750</v>
+        <v>128494710</v>
       </c>
       <c r="B8" t="n">
-        <v>86927</v>
+        <v>86890</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6003295</v>
+        <v>3674</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1373,10 +1373,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>629940</v>
+        <v>629987</v>
       </c>
       <c r="R8" t="n">
-        <v>6720267</v>
+        <v>6720190</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1436,10 +1436,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128494710</v>
+        <v>128482529</v>
       </c>
       <c r="B9" t="n">
-        <v>86890</v>
+        <v>86729</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1447,37 +1447,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>3674</v>
+        <v>3762</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Flät, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>629987</v>
+        <v>629954</v>
       </c>
       <c r="R9" t="n">
-        <v>6720190</v>
+        <v>6720288</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1518,7 +1515,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1537,10 +1533,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128482529</v>
+        <v>128482901</v>
       </c>
       <c r="B10" t="n">
-        <v>86729</v>
+        <v>86904</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1548,34 +1544,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>3762</v>
+        <v>249228</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Barrfagerspindling</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius piceae</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Frøslev &amp; al.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Flät, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>629954</v>
+        <v>629986</v>
       </c>
       <c r="R10" t="n">
-        <v>6720288</v>
+        <v>6720246</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1616,6 +1615,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1634,10 +1634,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128482901</v>
+        <v>128494737</v>
       </c>
       <c r="B11" t="n">
-        <v>86904</v>
+        <v>86729</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1645,21 +1645,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>249228</v>
+        <v>3762</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Barrfagerspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cortinarius piceae</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Frøslev &amp; al.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1672,10 +1672,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>629986</v>
+        <v>629913</v>
       </c>
       <c r="R11" t="n">
-        <v>6720246</v>
+        <v>6720256</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1735,48 +1735,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128494737</v>
+        <v>128481990</v>
       </c>
       <c r="B12" t="n">
-        <v>86729</v>
+        <v>92784</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>3762</v>
+        <v>5449</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Flät, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>629913</v>
+        <v>629885</v>
       </c>
       <c r="R12" t="n">
-        <v>6720256</v>
+        <v>6720262</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1817,7 +1814,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1836,10 +1832,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128481990</v>
+        <v>128482768</v>
       </c>
       <c r="B13" t="n">
-        <v>92784</v>
+        <v>86927</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1847,34 +1843,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5449</v>
+        <v>6003295</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Flät, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>629885</v>
+        <v>629958</v>
       </c>
       <c r="R13" t="n">
-        <v>6720262</v>
+        <v>6720276</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1915,6 +1914,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 30484-2025 artfynd.xlsx
+++ b/artfynd/A 30484-2025 artfynd.xlsx
@@ -1039,7 +1039,7 @@
         <v>128481937</v>
       </c>
       <c r="B5" t="n">
-        <v>91001</v>
+        <v>91002</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1133,32 +1133,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128494722</v>
+        <v>128494750</v>
       </c>
       <c r="B6" t="n">
-        <v>92768</v>
+        <v>86927</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4366</v>
+        <v>6003295</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1171,10 +1171,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>629919</v>
+        <v>629940</v>
       </c>
       <c r="R6" t="n">
-        <v>6720276</v>
+        <v>6720267</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1234,32 +1234,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128494750</v>
+        <v>128494722</v>
       </c>
       <c r="B7" t="n">
-        <v>86927</v>
+        <v>92769</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6003295</v>
+        <v>4366</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>629940</v>
+        <v>629919</v>
       </c>
       <c r="R7" t="n">
-        <v>6720267</v>
+        <v>6720276</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1436,10 +1436,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128482529</v>
+        <v>128482901</v>
       </c>
       <c r="B9" t="n">
-        <v>86729</v>
+        <v>86904</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1447,34 +1447,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>3762</v>
+        <v>249228</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Barrfagerspindling</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius piceae</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Frøslev &amp; al.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Flät, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>629954</v>
+        <v>629986</v>
       </c>
       <c r="R9" t="n">
-        <v>6720288</v>
+        <v>6720246</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1515,6 +1518,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1533,10 +1537,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128482901</v>
+        <v>128482529</v>
       </c>
       <c r="B10" t="n">
-        <v>86904</v>
+        <v>86729</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1544,37 +1548,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>249228</v>
+        <v>3762</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Barrfagerspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cortinarius piceae</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Frøslev &amp; al.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Flät, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>629986</v>
+        <v>629954</v>
       </c>
       <c r="R10" t="n">
-        <v>6720246</v>
+        <v>6720288</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1615,7 +1616,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1634,48 +1634,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128494737</v>
+        <v>128481990</v>
       </c>
       <c r="B11" t="n">
-        <v>86729</v>
+        <v>92785</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>3762</v>
+        <v>5449</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Flät, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>629913</v>
+        <v>629885</v>
       </c>
       <c r="R11" t="n">
-        <v>6720256</v>
+        <v>6720262</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1716,7 +1713,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1735,45 +1731,48 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128481990</v>
+        <v>128494737</v>
       </c>
       <c r="B12" t="n">
-        <v>92784</v>
+        <v>86729</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5449</v>
+        <v>3762</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Flät, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>629885</v>
+        <v>629913</v>
       </c>
       <c r="R12" t="n">
-        <v>6720262</v>
+        <v>6720256</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1814,6 +1813,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 30484-2025 artfynd.xlsx
+++ b/artfynd/A 30484-2025 artfynd.xlsx
@@ -1039,7 +1039,7 @@
         <v>128481937</v>
       </c>
       <c r="B5" t="n">
-        <v>91002</v>
+        <v>91029</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1133,32 +1133,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128494750</v>
+        <v>128494722</v>
       </c>
       <c r="B6" t="n">
-        <v>86927</v>
+        <v>92796</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6003295</v>
+        <v>4366</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1171,10 +1171,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>629940</v>
+        <v>629919</v>
       </c>
       <c r="R6" t="n">
-        <v>6720267</v>
+        <v>6720276</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1234,32 +1234,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128494722</v>
+        <v>128494750</v>
       </c>
       <c r="B7" t="n">
-        <v>92769</v>
+        <v>86954</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4366</v>
+        <v>6003295</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>629919</v>
+        <v>629940</v>
       </c>
       <c r="R7" t="n">
-        <v>6720276</v>
+        <v>6720267</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1338,7 +1338,7 @@
         <v>128494710</v>
       </c>
       <c r="B8" t="n">
-        <v>86890</v>
+        <v>86917</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1436,10 +1436,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128482901</v>
+        <v>128482529</v>
       </c>
       <c r="B9" t="n">
-        <v>86904</v>
+        <v>86756</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1447,37 +1447,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>249228</v>
+        <v>3762</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Barrfagerspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cortinarius piceae</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Frøslev &amp; al.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Flät, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>629986</v>
+        <v>629954</v>
       </c>
       <c r="R9" t="n">
-        <v>6720246</v>
+        <v>6720288</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1518,7 +1515,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1537,10 +1533,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128482529</v>
+        <v>128482901</v>
       </c>
       <c r="B10" t="n">
-        <v>86729</v>
+        <v>86931</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1548,34 +1544,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>3762</v>
+        <v>249228</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Barrfagerspindling</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius piceae</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Frøslev &amp; al.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Flät, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>629954</v>
+        <v>629986</v>
       </c>
       <c r="R10" t="n">
-        <v>6720288</v>
+        <v>6720246</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1616,6 +1615,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1637,7 +1637,7 @@
         <v>128481990</v>
       </c>
       <c r="B11" t="n">
-        <v>92785</v>
+        <v>92812</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1734,7 +1734,7 @@
         <v>128494737</v>
       </c>
       <c r="B12" t="n">
-        <v>86729</v>
+        <v>86756</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1835,7 +1835,7 @@
         <v>128482768</v>
       </c>
       <c r="B13" t="n">
-        <v>86927</v>
+        <v>86954</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 30484-2025 artfynd.xlsx
+++ b/artfynd/A 30484-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AY14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1039,7 +1039,7 @@
         <v>128481937</v>
       </c>
       <c r="B5" t="n">
-        <v>91029</v>
+        <v>91034</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1133,32 +1133,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128494722</v>
+        <v>128494750</v>
       </c>
       <c r="B6" t="n">
-        <v>92796</v>
+        <v>86958</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4366</v>
+        <v>6003295</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1171,10 +1171,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>629919</v>
+        <v>629940</v>
       </c>
       <c r="R6" t="n">
-        <v>6720276</v>
+        <v>6720267</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1234,32 +1234,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128494750</v>
+        <v>128494722</v>
       </c>
       <c r="B7" t="n">
-        <v>86954</v>
+        <v>92801</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6003295</v>
+        <v>4366</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>629940</v>
+        <v>629919</v>
       </c>
       <c r="R7" t="n">
-        <v>6720267</v>
+        <v>6720276</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1338,7 +1338,7 @@
         <v>128494710</v>
       </c>
       <c r="B8" t="n">
-        <v>86917</v>
+        <v>86921</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1436,10 +1436,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128482529</v>
+        <v>128482901</v>
       </c>
       <c r="B9" t="n">
-        <v>86756</v>
+        <v>86935</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1447,34 +1447,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>3762</v>
+        <v>249228</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Barrfagerspindling</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius piceae</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Frøslev &amp; al.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Flät, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>629954</v>
+        <v>629986</v>
       </c>
       <c r="R9" t="n">
-        <v>6720288</v>
+        <v>6720246</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1515,6 +1518,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1533,10 +1537,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128482901</v>
+        <v>128482529</v>
       </c>
       <c r="B10" t="n">
-        <v>86931</v>
+        <v>86760</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1544,37 +1548,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>249228</v>
+        <v>3762</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Barrfagerspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cortinarius piceae</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Frøslev &amp; al.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Flät, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>629986</v>
+        <v>629954</v>
       </c>
       <c r="R10" t="n">
-        <v>6720246</v>
+        <v>6720288</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1615,7 +1616,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1637,7 +1637,7 @@
         <v>128481990</v>
       </c>
       <c r="B11" t="n">
-        <v>92812</v>
+        <v>92817</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1734,7 +1734,7 @@
         <v>128494737</v>
       </c>
       <c r="B12" t="n">
-        <v>86756</v>
+        <v>86760</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1835,7 +1835,7 @@
         <v>128482768</v>
       </c>
       <c r="B13" t="n">
-        <v>86954</v>
+        <v>86958</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1931,6 +1931,103 @@
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>128885154</v>
+      </c>
+      <c r="B14" t="n">
+        <v>92803</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6047725</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Rödfläckig zontaggsvamp</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Hydnellum rufoconcrescens nom.prov.</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Flät, Upl</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>629954</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6720288</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 30484-2025 artfynd.xlsx
+++ b/artfynd/A 30484-2025 artfynd.xlsx
@@ -1039,7 +1039,7 @@
         <v>128481937</v>
       </c>
       <c r="B5" t="n">
-        <v>91034</v>
+        <v>91039</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
         <v>128494750</v>
       </c>
       <c r="B6" t="n">
-        <v>86958</v>
+        <v>86959</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1237,7 +1237,7 @@
         <v>128494722</v>
       </c>
       <c r="B7" t="n">
-        <v>92801</v>
+        <v>92806</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1338,7 +1338,7 @@
         <v>128494710</v>
       </c>
       <c r="B8" t="n">
-        <v>86921</v>
+        <v>86922</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1439,7 +1439,7 @@
         <v>128482901</v>
       </c>
       <c r="B9" t="n">
-        <v>86935</v>
+        <v>86936</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>128481990</v>
       </c>
       <c r="B11" t="n">
-        <v>92817</v>
+        <v>92823</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1647,21 +1647,12 @@
       <c r="E11" t="n">
         <v>5449</v>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Svart taggsvamp</t>
-        </is>
-      </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
+          <t>Phellodon niger s.lat</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1835,7 +1826,7 @@
         <v>128482768</v>
       </c>
       <c r="B13" t="n">
-        <v>86958</v>
+        <v>86959</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1936,7 +1927,7 @@
         <v>128885154</v>
       </c>
       <c r="B14" t="n">
-        <v>92803</v>
+        <v>92808</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 30484-2025 artfynd.xlsx
+++ b/artfynd/A 30484-2025 artfynd.xlsx
@@ -1133,32 +1133,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128494750</v>
+        <v>128494722</v>
       </c>
       <c r="B6" t="n">
-        <v>86959</v>
+        <v>92806</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6003295</v>
+        <v>4366</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1171,10 +1171,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>629940</v>
+        <v>629919</v>
       </c>
       <c r="R6" t="n">
-        <v>6720267</v>
+        <v>6720276</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1234,32 +1234,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128494722</v>
+        <v>128494750</v>
       </c>
       <c r="B7" t="n">
-        <v>92806</v>
+        <v>86959</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4366</v>
+        <v>6003295</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>629919</v>
+        <v>629940</v>
       </c>
       <c r="R7" t="n">
-        <v>6720276</v>
+        <v>6720267</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1436,10 +1436,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128482901</v>
+        <v>128482529</v>
       </c>
       <c r="B9" t="n">
-        <v>86936</v>
+        <v>86760</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1447,37 +1447,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>249228</v>
+        <v>3762</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Barrfagerspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cortinarius piceae</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Frøslev &amp; al.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Flät, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>629986</v>
+        <v>629954</v>
       </c>
       <c r="R9" t="n">
-        <v>6720246</v>
+        <v>6720288</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1518,7 +1515,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1537,10 +1533,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128482529</v>
+        <v>128482901</v>
       </c>
       <c r="B10" t="n">
-        <v>86760</v>
+        <v>86936</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1548,34 +1544,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>3762</v>
+        <v>249228</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Barrfagerspindling</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius piceae</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Frøslev &amp; al.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Flät, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>629954</v>
+        <v>629986</v>
       </c>
       <c r="R10" t="n">
-        <v>6720288</v>
+        <v>6720246</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1616,6 +1615,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 30484-2025 artfynd.xlsx
+++ b/artfynd/A 30484-2025 artfynd.xlsx
@@ -1039,7 +1039,7 @@
         <v>128481937</v>
       </c>
       <c r="B5" t="n">
-        <v>91039</v>
+        <v>91043</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
         <v>128494722</v>
       </c>
       <c r="B6" t="n">
-        <v>92806</v>
+        <v>92810</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1237,7 +1237,7 @@
         <v>128494750</v>
       </c>
       <c r="B7" t="n">
-        <v>86959</v>
+        <v>86963</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1338,7 +1338,7 @@
         <v>128494710</v>
       </c>
       <c r="B8" t="n">
-        <v>86922</v>
+        <v>86926</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1436,10 +1436,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128482529</v>
+        <v>128482901</v>
       </c>
       <c r="B9" t="n">
-        <v>86760</v>
+        <v>86940</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1447,34 +1447,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>3762</v>
+        <v>249228</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Barrfagerspindling</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius piceae</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Frøslev &amp; al.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Flät, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>629954</v>
+        <v>629986</v>
       </c>
       <c r="R9" t="n">
-        <v>6720288</v>
+        <v>6720246</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1515,6 +1518,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1533,10 +1537,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128482901</v>
+        <v>128482529</v>
       </c>
       <c r="B10" t="n">
-        <v>86936</v>
+        <v>86764</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1544,37 +1548,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>249228</v>
+        <v>3762</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Barrfagerspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cortinarius piceae</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Frøslev &amp; al.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Flät, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>629986</v>
+        <v>629954</v>
       </c>
       <c r="R10" t="n">
-        <v>6720246</v>
+        <v>6720288</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1615,7 +1616,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1634,36 +1634,48 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128481990</v>
+        <v>128494737</v>
       </c>
       <c r="B11" t="n">
-        <v>92823</v>
+        <v>86764</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5449</v>
+        <v>3762</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Olivspindling</t>
+        </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr"/>
+          <t>Cortinarius venetus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) Fr.</t>
+        </is>
+      </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Flät, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>629885</v>
+        <v>629913</v>
       </c>
       <c r="R11" t="n">
-        <v>6720262</v>
+        <v>6720256</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1704,6 +1716,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1722,48 +1735,36 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128494737</v>
+        <v>128481990</v>
       </c>
       <c r="B12" t="n">
-        <v>86760</v>
+        <v>92827</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>3762</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Olivspindling</t>
-        </is>
+        <v>5449</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>(Fr.:Fr.) Fr.</t>
-        </is>
-      </c>
+          <t>Phellodon niger s.lat</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Flät, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>629913</v>
+        <v>629885</v>
       </c>
       <c r="R12" t="n">
-        <v>6720256</v>
+        <v>6720262</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1804,7 +1805,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1826,7 +1826,7 @@
         <v>128482768</v>
       </c>
       <c r="B13" t="n">
-        <v>86959</v>
+        <v>86963</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1927,7 +1927,7 @@
         <v>128885154</v>
       </c>
       <c r="B14" t="n">
-        <v>92808</v>
+        <v>92812</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 30484-2025 artfynd.xlsx
+++ b/artfynd/A 30484-2025 artfynd.xlsx
@@ -1436,10 +1436,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128482901</v>
+        <v>128482529</v>
       </c>
       <c r="B9" t="n">
-        <v>86940</v>
+        <v>86764</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1447,37 +1447,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>249228</v>
+        <v>3762</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Barrfagerspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cortinarius piceae</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Frøslev &amp; al.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Flät, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>629986</v>
+        <v>629954</v>
       </c>
       <c r="R9" t="n">
-        <v>6720246</v>
+        <v>6720288</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1518,7 +1515,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1537,10 +1533,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128482529</v>
+        <v>128482901</v>
       </c>
       <c r="B10" t="n">
-        <v>86764</v>
+        <v>86940</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1548,34 +1544,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>3762</v>
+        <v>249228</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Barrfagerspindling</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius piceae</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Frøslev &amp; al.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Flät, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>629954</v>
+        <v>629986</v>
       </c>
       <c r="R10" t="n">
-        <v>6720288</v>
+        <v>6720246</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1616,6 +1615,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1634,48 +1634,36 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128494737</v>
+        <v>128481990</v>
       </c>
       <c r="B11" t="n">
-        <v>86764</v>
+        <v>92827</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>3762</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Olivspindling</t>
-        </is>
+        <v>5449</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>(Fr.:Fr.) Fr.</t>
-        </is>
-      </c>
+          <t>Phellodon niger s.lat</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Flät, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>629913</v>
+        <v>629885</v>
       </c>
       <c r="R11" t="n">
-        <v>6720256</v>
+        <v>6720262</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1716,7 +1704,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1735,36 +1722,48 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128481990</v>
+        <v>128494737</v>
       </c>
       <c r="B12" t="n">
-        <v>92827</v>
+        <v>86764</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5449</v>
+        <v>3762</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Olivspindling</t>
+        </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr"/>
+          <t>Cortinarius venetus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) Fr.</t>
+        </is>
+      </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Flät, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>629885</v>
+        <v>629913</v>
       </c>
       <c r="R12" t="n">
-        <v>6720262</v>
+        <v>6720256</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1805,6 +1804,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 30484-2025 artfynd.xlsx
+++ b/artfynd/A 30484-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AY20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1133,32 +1133,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128494722</v>
+        <v>128494750</v>
       </c>
       <c r="B6" t="n">
-        <v>92810</v>
+        <v>86963</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4366</v>
+        <v>6003295</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1171,10 +1171,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>629919</v>
+        <v>629940</v>
       </c>
       <c r="R6" t="n">
-        <v>6720276</v>
+        <v>6720267</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1234,32 +1234,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128494750</v>
+        <v>128494722</v>
       </c>
       <c r="B7" t="n">
-        <v>86963</v>
+        <v>92810</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6003295</v>
+        <v>4366</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>629940</v>
+        <v>629919</v>
       </c>
       <c r="R7" t="n">
-        <v>6720267</v>
+        <v>6720276</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1436,10 +1436,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128482529</v>
+        <v>128482901</v>
       </c>
       <c r="B9" t="n">
-        <v>86764</v>
+        <v>86940</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1447,34 +1447,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>3762</v>
+        <v>249228</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Barrfagerspindling</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius piceae</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Frøslev &amp; al.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Flät, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>629954</v>
+        <v>629986</v>
       </c>
       <c r="R9" t="n">
-        <v>6720288</v>
+        <v>6720246</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1515,6 +1518,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1533,10 +1537,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128482901</v>
+        <v>128482529</v>
       </c>
       <c r="B10" t="n">
-        <v>86940</v>
+        <v>86764</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1544,37 +1548,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>249228</v>
+        <v>3762</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Barrfagerspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cortinarius piceae</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Frøslev &amp; al.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Flät, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>629986</v>
+        <v>629954</v>
       </c>
       <c r="R10" t="n">
-        <v>6720246</v>
+        <v>6720288</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1615,7 +1616,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1634,36 +1634,48 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128481990</v>
+        <v>128494737</v>
       </c>
       <c r="B11" t="n">
-        <v>92827</v>
+        <v>86764</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5449</v>
+        <v>3762</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Olivspindling</t>
+        </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr"/>
+          <t>Cortinarius venetus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) Fr.</t>
+        </is>
+      </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Flät, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>629885</v>
+        <v>629913</v>
       </c>
       <c r="R11" t="n">
-        <v>6720262</v>
+        <v>6720256</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1704,6 +1716,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1722,48 +1735,36 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128494737</v>
+        <v>128481990</v>
       </c>
       <c r="B12" t="n">
-        <v>86764</v>
+        <v>92827</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>3762</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Olivspindling</t>
-        </is>
+        <v>5449</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>(Fr.:Fr.) Fr.</t>
-        </is>
-      </c>
+          <t>Phellodon niger s.lat</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Flät, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>629913</v>
+        <v>629885</v>
       </c>
       <c r="R12" t="n">
-        <v>6720256</v>
+        <v>6720262</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1804,7 +1805,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -2019,6 +2019,596 @@
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>128952919</v>
+      </c>
+      <c r="B15" t="n">
+        <v>86906</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>473</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Äggspindling</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Cortinarius meinhardii</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Bon</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Flät, Upl</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>629934</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6720275</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>128952903</v>
+      </c>
+      <c r="B16" t="n">
+        <v>86855</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>445</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Kopparspindling</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Cortinarius cupreorufus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Brandrud</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Flät, Upl</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>629919</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6720276</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>128936574</v>
+      </c>
+      <c r="B17" t="n">
+        <v>92262</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>232138</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Gul lammticka</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Albatrellus citrinus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Ryman</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Flät, Upl</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>629919</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6720276</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>128935482</v>
+      </c>
+      <c r="B18" t="n">
+        <v>86992</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>3739</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Persiljespindling</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Cortinarius sulfurinus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Quél.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Flät, Upl</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>629912</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6720245</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>128953115</v>
+      </c>
+      <c r="B19" t="n">
+        <v>86963</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Flät, Upl</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>629919</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6720276</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>128936491</v>
+      </c>
+      <c r="B20" t="n">
+        <v>87020</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>433</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Duvspindling</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Cortinarius caesiocanescens s.lat.</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Flät, Upl</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>629932</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6720234</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 30484-2025 artfynd.xlsx
+++ b/artfynd/A 30484-2025 artfynd.xlsx
@@ -1039,7 +1039,7 @@
         <v>128481937</v>
       </c>
       <c r="B5" t="n">
-        <v>91043</v>
+        <v>91048</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
         <v>128494750</v>
       </c>
       <c r="B6" t="n">
-        <v>86963</v>
+        <v>86968</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1237,7 +1237,7 @@
         <v>128494722</v>
       </c>
       <c r="B7" t="n">
-        <v>92810</v>
+        <v>92815</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1338,7 +1338,7 @@
         <v>128494710</v>
       </c>
       <c r="B8" t="n">
-        <v>86926</v>
+        <v>86931</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1439,7 +1439,7 @@
         <v>128482901</v>
       </c>
       <c r="B9" t="n">
-        <v>86940</v>
+        <v>86945</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1540,7 +1540,7 @@
         <v>128482529</v>
       </c>
       <c r="B10" t="n">
-        <v>86764</v>
+        <v>86769</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>128494737</v>
       </c>
       <c r="B11" t="n">
-        <v>86764</v>
+        <v>86769</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1738,7 +1738,7 @@
         <v>128481990</v>
       </c>
       <c r="B12" t="n">
-        <v>92827</v>
+        <v>92832</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1826,7 +1826,7 @@
         <v>128482768</v>
       </c>
       <c r="B13" t="n">
-        <v>86963</v>
+        <v>86968</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1927,7 +1927,7 @@
         <v>128885154</v>
       </c>
       <c r="B14" t="n">
-        <v>92812</v>
+        <v>92817</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2024,7 +2024,7 @@
         <v>128952919</v>
       </c>
       <c r="B15" t="n">
-        <v>86906</v>
+        <v>86911</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2125,7 +2125,7 @@
         <v>128952903</v>
       </c>
       <c r="B16" t="n">
-        <v>86855</v>
+        <v>86860</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2226,7 +2226,7 @@
         <v>128936574</v>
       </c>
       <c r="B17" t="n">
-        <v>92262</v>
+        <v>92267</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2323,7 +2323,7 @@
         <v>128935482</v>
       </c>
       <c r="B18" t="n">
-        <v>86992</v>
+        <v>86997</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2420,7 +2420,7 @@
         <v>128953115</v>
       </c>
       <c r="B19" t="n">
-        <v>86963</v>
+        <v>86968</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2521,7 +2521,7 @@
         <v>128936491</v>
       </c>
       <c r="B20" t="n">
-        <v>87020</v>
+        <v>87025</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 30484-2025 artfynd.xlsx
+++ b/artfynd/A 30484-2025 artfynd.xlsx
@@ -1039,7 +1039,7 @@
         <v>128481937</v>
       </c>
       <c r="B5" t="n">
-        <v>91050</v>
+        <v>91055</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1133,32 +1133,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128494722</v>
+        <v>128494750</v>
       </c>
       <c r="B6" t="n">
-        <v>92818</v>
+        <v>86975</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4366</v>
+        <v>6003295</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1171,10 +1171,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>629919</v>
+        <v>629940</v>
       </c>
       <c r="R6" t="n">
-        <v>6720276</v>
+        <v>6720267</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1234,32 +1234,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128494750</v>
+        <v>128494722</v>
       </c>
       <c r="B7" t="n">
-        <v>86970</v>
+        <v>92823</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6003295</v>
+        <v>4366</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>629940</v>
+        <v>629919</v>
       </c>
       <c r="R7" t="n">
-        <v>6720267</v>
+        <v>6720276</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1338,7 +1338,7 @@
         <v>128494710</v>
       </c>
       <c r="B8" t="n">
-        <v>86933</v>
+        <v>86938</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1436,10 +1436,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128482529</v>
+        <v>128482901</v>
       </c>
       <c r="B9" t="n">
-        <v>86771</v>
+        <v>86952</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1447,34 +1447,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>3762</v>
+        <v>249228</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Barrfagerspindling</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius piceae</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Frøslev &amp; al.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Flät, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>629954</v>
+        <v>629986</v>
       </c>
       <c r="R9" t="n">
-        <v>6720288</v>
+        <v>6720246</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1515,6 +1518,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1533,10 +1537,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128482901</v>
+        <v>128482529</v>
       </c>
       <c r="B10" t="n">
-        <v>86947</v>
+        <v>86776</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1544,37 +1548,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>249228</v>
+        <v>3762</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Barrfagerspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cortinarius piceae</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Frøslev &amp; al.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Flät, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>629986</v>
+        <v>629954</v>
       </c>
       <c r="R10" t="n">
-        <v>6720246</v>
+        <v>6720288</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1615,7 +1616,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1634,48 +1634,36 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128494737</v>
+        <v>128481990</v>
       </c>
       <c r="B11" t="n">
-        <v>86771</v>
+        <v>92840</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>3762</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Olivspindling</t>
-        </is>
+        <v>5449</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>(Fr.:Fr.) Fr.</t>
-        </is>
-      </c>
+          <t>Phellodon niger s.lat</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Flät, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>629913</v>
+        <v>629885</v>
       </c>
       <c r="R11" t="n">
-        <v>6720256</v>
+        <v>6720262</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1716,7 +1704,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1735,36 +1722,48 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128481990</v>
+        <v>128494737</v>
       </c>
       <c r="B12" t="n">
-        <v>92835</v>
+        <v>86776</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5449</v>
+        <v>3762</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Olivspindling</t>
+        </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr"/>
+          <t>Cortinarius venetus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) Fr.</t>
+        </is>
+      </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Flät, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>629885</v>
+        <v>629913</v>
       </c>
       <c r="R12" t="n">
-        <v>6720262</v>
+        <v>6720256</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1805,6 +1804,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 30484-2025 artfynd.xlsx
+++ b/artfynd/A 30484-2025 artfynd.xlsx
@@ -1133,32 +1133,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128494750</v>
+        <v>128494722</v>
       </c>
       <c r="B6" t="n">
-        <v>86975</v>
+        <v>92823</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6003295</v>
+        <v>4366</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1171,10 +1171,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>629940</v>
+        <v>629919</v>
       </c>
       <c r="R6" t="n">
-        <v>6720267</v>
+        <v>6720276</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1234,32 +1234,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128494722</v>
+        <v>128494750</v>
       </c>
       <c r="B7" t="n">
-        <v>92823</v>
+        <v>86975</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4366</v>
+        <v>6003295</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>629919</v>
+        <v>629940</v>
       </c>
       <c r="R7" t="n">
-        <v>6720276</v>
+        <v>6720267</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1436,10 +1436,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128482901</v>
+        <v>128482529</v>
       </c>
       <c r="B9" t="n">
-        <v>86952</v>
+        <v>86776</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1447,37 +1447,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>249228</v>
+        <v>3762</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Barrfagerspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cortinarius piceae</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Frøslev &amp; al.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Flät, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>629986</v>
+        <v>629954</v>
       </c>
       <c r="R9" t="n">
-        <v>6720246</v>
+        <v>6720288</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1518,7 +1515,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1537,10 +1533,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128482529</v>
+        <v>128482901</v>
       </c>
       <c r="B10" t="n">
-        <v>86776</v>
+        <v>86952</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1548,34 +1544,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>3762</v>
+        <v>249228</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Barrfagerspindling</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius piceae</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Frøslev &amp; al.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Flät, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>629954</v>
+        <v>629986</v>
       </c>
       <c r="R10" t="n">
-        <v>6720288</v>
+        <v>6720246</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1616,6 +1615,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1634,36 +1634,48 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128481990</v>
+        <v>128494737</v>
       </c>
       <c r="B11" t="n">
-        <v>92840</v>
+        <v>86776</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5449</v>
+        <v>3762</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Olivspindling</t>
+        </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr"/>
+          <t>Cortinarius venetus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) Fr.</t>
+        </is>
+      </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Flät, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>629885</v>
+        <v>629913</v>
       </c>
       <c r="R11" t="n">
-        <v>6720262</v>
+        <v>6720256</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1704,6 +1716,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1722,48 +1735,36 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128494737</v>
+        <v>128481990</v>
       </c>
       <c r="B12" t="n">
-        <v>86776</v>
+        <v>92840</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>3762</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Olivspindling</t>
-        </is>
+        <v>5449</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>(Fr.:Fr.) Fr.</t>
-        </is>
-      </c>
+          <t>Phellodon niger s.lat</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Flät, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>629913</v>
+        <v>629885</v>
       </c>
       <c r="R12" t="n">
-        <v>6720256</v>
+        <v>6720262</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1804,7 +1805,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1826,7 +1826,7 @@
         <v>128482768</v>
       </c>
       <c r="B13" t="n">
-        <v>86975</v>
+        <v>86978</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1927,7 +1927,7 @@
         <v>128885154</v>
       </c>
       <c r="B14" t="n">
-        <v>92825</v>
+        <v>92830</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2024,7 +2024,7 @@
         <v>128952919</v>
       </c>
       <c r="B15" t="n">
-        <v>86918</v>
+        <v>86921</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2125,7 +2125,7 @@
         <v>128952903</v>
       </c>
       <c r="B16" t="n">
-        <v>86867</v>
+        <v>86870</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2226,7 +2226,7 @@
         <v>128936574</v>
       </c>
       <c r="B17" t="n">
-        <v>92275</v>
+        <v>92280</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2323,7 +2323,7 @@
         <v>128935482</v>
       </c>
       <c r="B18" t="n">
-        <v>87004</v>
+        <v>87007</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2420,7 +2420,7 @@
         <v>128953115</v>
       </c>
       <c r="B19" t="n">
-        <v>86975</v>
+        <v>86978</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2521,7 +2521,7 @@
         <v>128936491</v>
       </c>
       <c r="B20" t="n">
-        <v>87032</v>
+        <v>87035</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 30484-2025 artfynd.xlsx
+++ b/artfynd/A 30484-2025 artfynd.xlsx
@@ -1039,7 +1039,7 @@
         <v>128481937</v>
       </c>
       <c r="B5" t="n">
-        <v>91055</v>
+        <v>91061</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
         <v>128494722</v>
       </c>
       <c r="B6" t="n">
-        <v>92823</v>
+        <v>92831</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1237,7 +1237,7 @@
         <v>128494750</v>
       </c>
       <c r="B7" t="n">
-        <v>86975</v>
+        <v>86981</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1338,7 +1338,7 @@
         <v>128494710</v>
       </c>
       <c r="B8" t="n">
-        <v>86938</v>
+        <v>86944</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1436,10 +1436,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128482529</v>
+        <v>128482901</v>
       </c>
       <c r="B9" t="n">
-        <v>86776</v>
+        <v>86958</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1447,34 +1447,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>3762</v>
+        <v>249228</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Barrfagerspindling</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius piceae</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Frøslev &amp; al.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Flät, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>629954</v>
+        <v>629986</v>
       </c>
       <c r="R9" t="n">
-        <v>6720288</v>
+        <v>6720246</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1515,6 +1518,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1533,10 +1537,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128482901</v>
+        <v>128482529</v>
       </c>
       <c r="B10" t="n">
-        <v>86952</v>
+        <v>86782</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1544,37 +1548,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>249228</v>
+        <v>3762</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Barrfagerspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cortinarius piceae</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Frøslev &amp; al.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Flät, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>629986</v>
+        <v>629954</v>
       </c>
       <c r="R10" t="n">
-        <v>6720246</v>
+        <v>6720288</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1615,7 +1616,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1637,7 +1637,7 @@
         <v>128494737</v>
       </c>
       <c r="B11" t="n">
-        <v>86776</v>
+        <v>86782</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1738,7 +1738,7 @@
         <v>128481990</v>
       </c>
       <c r="B12" t="n">
-        <v>92840</v>
+        <v>92848</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1826,7 +1826,7 @@
         <v>128482768</v>
       </c>
       <c r="B13" t="n">
-        <v>86978</v>
+        <v>86981</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1927,7 +1927,7 @@
         <v>128885154</v>
       </c>
       <c r="B14" t="n">
-        <v>92830</v>
+        <v>92833</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2024,7 +2024,7 @@
         <v>128952919</v>
       </c>
       <c r="B15" t="n">
-        <v>86921</v>
+        <v>86924</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2125,7 +2125,7 @@
         <v>128952903</v>
       </c>
       <c r="B16" t="n">
-        <v>86870</v>
+        <v>86873</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2226,7 +2226,7 @@
         <v>128936574</v>
       </c>
       <c r="B17" t="n">
-        <v>92280</v>
+        <v>92283</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2323,7 +2323,7 @@
         <v>128935482</v>
       </c>
       <c r="B18" t="n">
-        <v>87007</v>
+        <v>87010</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2420,7 +2420,7 @@
         <v>128953115</v>
       </c>
       <c r="B19" t="n">
-        <v>86978</v>
+        <v>86981</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2521,7 +2521,7 @@
         <v>128936491</v>
       </c>
       <c r="B20" t="n">
-        <v>87035</v>
+        <v>87038</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 30484-2025 artfynd.xlsx
+++ b/artfynd/A 30484-2025 artfynd.xlsx
@@ -1826,7 +1826,7 @@
         <v>128482768</v>
       </c>
       <c r="B13" t="n">
-        <v>86981</v>
+        <v>86985</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1927,7 +1927,7 @@
         <v>128885154</v>
       </c>
       <c r="B14" t="n">
-        <v>92833</v>
+        <v>92840</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2024,7 +2024,7 @@
         <v>128952919</v>
       </c>
       <c r="B15" t="n">
-        <v>86924</v>
+        <v>86928</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2125,7 +2125,7 @@
         <v>128952903</v>
       </c>
       <c r="B16" t="n">
-        <v>86873</v>
+        <v>86877</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2226,7 +2226,7 @@
         <v>128936574</v>
       </c>
       <c r="B17" t="n">
-        <v>92283</v>
+        <v>92290</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2323,7 +2323,7 @@
         <v>128935482</v>
       </c>
       <c r="B18" t="n">
-        <v>87010</v>
+        <v>87014</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2420,7 +2420,7 @@
         <v>128953115</v>
       </c>
       <c r="B19" t="n">
-        <v>86981</v>
+        <v>86985</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2521,7 +2521,7 @@
         <v>128936491</v>
       </c>
       <c r="B20" t="n">
-        <v>87038</v>
+        <v>87042</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 30484-2025 artfynd.xlsx
+++ b/artfynd/A 30484-2025 artfynd.xlsx
@@ -1927,7 +1927,7 @@
         <v>128885154</v>
       </c>
       <c r="B14" t="n">
-        <v>92840</v>
+        <v>92847</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2024,7 +2024,7 @@
         <v>128952919</v>
       </c>
       <c r="B15" t="n">
-        <v>86928</v>
+        <v>86935</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2125,7 +2125,7 @@
         <v>128952903</v>
       </c>
       <c r="B16" t="n">
-        <v>86877</v>
+        <v>86884</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2226,7 +2226,7 @@
         <v>128936574</v>
       </c>
       <c r="B17" t="n">
-        <v>92290</v>
+        <v>92297</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2323,7 +2323,7 @@
         <v>128935482</v>
       </c>
       <c r="B18" t="n">
-        <v>87014</v>
+        <v>87021</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2420,7 +2420,7 @@
         <v>128953115</v>
       </c>
       <c r="B19" t="n">
-        <v>86985</v>
+        <v>86992</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2521,7 +2521,7 @@
         <v>128936491</v>
       </c>
       <c r="B20" t="n">
-        <v>87042</v>
+        <v>87049</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 30484-2025 artfynd.xlsx
+++ b/artfynd/A 30484-2025 artfynd.xlsx
@@ -1826,7 +1826,7 @@
         <v>128482768</v>
       </c>
       <c r="B13" t="n">
-        <v>86985</v>
+        <v>86994</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1927,7 +1927,7 @@
         <v>128885154</v>
       </c>
       <c r="B14" t="n">
-        <v>92847</v>
+        <v>92849</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2024,7 +2024,7 @@
         <v>128952919</v>
       </c>
       <c r="B15" t="n">
-        <v>86935</v>
+        <v>86937</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2125,7 +2125,7 @@
         <v>128952903</v>
       </c>
       <c r="B16" t="n">
-        <v>86884</v>
+        <v>86886</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2226,7 +2226,7 @@
         <v>128936574</v>
       </c>
       <c r="B17" t="n">
-        <v>92297</v>
+        <v>92299</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2323,7 +2323,7 @@
         <v>128935482</v>
       </c>
       <c r="B18" t="n">
-        <v>87021</v>
+        <v>87023</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2420,7 +2420,7 @@
         <v>128953115</v>
       </c>
       <c r="B19" t="n">
-        <v>86992</v>
+        <v>86994</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2521,7 +2521,7 @@
         <v>128936491</v>
       </c>
       <c r="B20" t="n">
-        <v>87049</v>
+        <v>87051</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 30484-2025 artfynd.xlsx
+++ b/artfynd/A 30484-2025 artfynd.xlsx
@@ -1927,7 +1927,7 @@
         <v>128885154</v>
       </c>
       <c r="B14" t="n">
-        <v>92849</v>
+        <v>92835</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2024,7 +2024,7 @@
         <v>128952919</v>
       </c>
       <c r="B15" t="n">
-        <v>86937</v>
+        <v>86938</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2125,7 +2125,7 @@
         <v>128952903</v>
       </c>
       <c r="B16" t="n">
-        <v>86886</v>
+        <v>86887</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2226,7 +2226,7 @@
         <v>128936574</v>
       </c>
       <c r="B17" t="n">
-        <v>92299</v>
+        <v>92313</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2323,7 +2323,7 @@
         <v>128935482</v>
       </c>
       <c r="B18" t="n">
-        <v>87023</v>
+        <v>87024</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2420,7 +2420,7 @@
         <v>128953115</v>
       </c>
       <c r="B19" t="n">
-        <v>86994</v>
+        <v>86995</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2521,7 +2521,7 @@
         <v>128936491</v>
       </c>
       <c r="B20" t="n">
-        <v>87051</v>
+        <v>87052</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 30484-2025 artfynd.xlsx
+++ b/artfynd/A 30484-2025 artfynd.xlsx
@@ -1927,7 +1927,7 @@
         <v>128885154</v>
       </c>
       <c r="B14" t="n">
-        <v>92835</v>
+        <v>92836</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2226,7 +2226,7 @@
         <v>128936574</v>
       </c>
       <c r="B17" t="n">
-        <v>92313</v>
+        <v>92314</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 30484-2025 artfynd.xlsx
+++ b/artfynd/A 30484-2025 artfynd.xlsx
@@ -1927,7 +1927,7 @@
         <v>128885154</v>
       </c>
       <c r="B14" t="n">
-        <v>92836</v>
+        <v>92839</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2024,7 +2024,7 @@
         <v>128952919</v>
       </c>
       <c r="B15" t="n">
-        <v>86938</v>
+        <v>86941</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2125,7 +2125,7 @@
         <v>128952903</v>
       </c>
       <c r="B16" t="n">
-        <v>86887</v>
+        <v>86890</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2226,7 +2226,7 @@
         <v>128936574</v>
       </c>
       <c r="B17" t="n">
-        <v>92314</v>
+        <v>92317</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2323,7 +2323,7 @@
         <v>128935482</v>
       </c>
       <c r="B18" t="n">
-        <v>87024</v>
+        <v>87027</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2420,7 +2420,7 @@
         <v>128953115</v>
       </c>
       <c r="B19" t="n">
-        <v>86995</v>
+        <v>86998</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2521,7 +2521,7 @@
         <v>128936491</v>
       </c>
       <c r="B20" t="n">
-        <v>87052</v>
+        <v>87055</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 30484-2025 artfynd.xlsx
+++ b/artfynd/A 30484-2025 artfynd.xlsx
@@ -2024,7 +2024,7 @@
         <v>128952919</v>
       </c>
       <c r="B15" t="n">
-        <v>86941</v>
+        <v>86943</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2125,7 +2125,7 @@
         <v>128952903</v>
       </c>
       <c r="B16" t="n">
-        <v>86890</v>
+        <v>86892</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2226,7 +2226,7 @@
         <v>128936574</v>
       </c>
       <c r="B17" t="n">
-        <v>92317</v>
+        <v>92319</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2323,7 +2323,7 @@
         <v>128935482</v>
       </c>
       <c r="B18" t="n">
-        <v>87027</v>
+        <v>87029</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2420,7 +2420,7 @@
         <v>128953115</v>
       </c>
       <c r="B19" t="n">
-        <v>86998</v>
+        <v>87000</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2521,7 +2521,7 @@
         <v>128936491</v>
       </c>
       <c r="B20" t="n">
-        <v>87055</v>
+        <v>87057</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 30484-2025 artfynd.xlsx
+++ b/artfynd/A 30484-2025 artfynd.xlsx
@@ -2024,7 +2024,7 @@
         <v>128952919</v>
       </c>
       <c r="B15" t="n">
-        <v>86943</v>
+        <v>86947</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2125,7 +2125,7 @@
         <v>128952903</v>
       </c>
       <c r="B16" t="n">
-        <v>86892</v>
+        <v>86896</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2226,7 +2226,7 @@
         <v>128936574</v>
       </c>
       <c r="B17" t="n">
-        <v>92319</v>
+        <v>92323</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2323,7 +2323,7 @@
         <v>128935482</v>
       </c>
       <c r="B18" t="n">
-        <v>87029</v>
+        <v>87033</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2420,7 +2420,7 @@
         <v>128953115</v>
       </c>
       <c r="B19" t="n">
-        <v>87000</v>
+        <v>87004</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2521,7 +2521,7 @@
         <v>128936491</v>
       </c>
       <c r="B20" t="n">
-        <v>87057</v>
+        <v>87061</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 30484-2025 artfynd.xlsx
+++ b/artfynd/A 30484-2025 artfynd.xlsx
@@ -2024,7 +2024,7 @@
         <v>128952919</v>
       </c>
       <c r="B15" t="n">
-        <v>86947</v>
+        <v>86948</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2125,7 +2125,7 @@
         <v>128952903</v>
       </c>
       <c r="B16" t="n">
-        <v>86896</v>
+        <v>86897</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2226,7 +2226,7 @@
         <v>128936574</v>
       </c>
       <c r="B17" t="n">
-        <v>92323</v>
+        <v>92324</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2323,7 +2323,7 @@
         <v>128935482</v>
       </c>
       <c r="B18" t="n">
-        <v>87033</v>
+        <v>87034</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2420,7 +2420,7 @@
         <v>128953115</v>
       </c>
       <c r="B19" t="n">
-        <v>87004</v>
+        <v>87005</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2521,7 +2521,7 @@
         <v>128936491</v>
       </c>
       <c r="B20" t="n">
-        <v>87061</v>
+        <v>87062</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 30484-2025 artfynd.xlsx
+++ b/artfynd/A 30484-2025 artfynd.xlsx
@@ -2226,7 +2226,7 @@
         <v>128936574</v>
       </c>
       <c r="B17" t="n">
-        <v>92324</v>
+        <v>92327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 30484-2025 artfynd.xlsx
+++ b/artfynd/A 30484-2025 artfynd.xlsx
@@ -2614,7 +2614,7 @@
         <v>132087861</v>
       </c>
       <c r="B21" t="n">
-        <v>87152</v>
+        <v>87155</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2723,7 +2723,7 @@
         <v>132087856</v>
       </c>
       <c r="B22" t="n">
-        <v>87152</v>
+        <v>87155</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2832,7 +2832,7 @@
         <v>132087872</v>
       </c>
       <c r="B23" t="n">
-        <v>87128</v>
+        <v>87131</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2933,7 +2933,7 @@
         <v>132087922</v>
       </c>
       <c r="B24" t="n">
-        <v>91415</v>
+        <v>91418</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 30484-2025 artfynd.xlsx
+++ b/artfynd/A 30484-2025 artfynd.xlsx
@@ -2614,7 +2614,7 @@
         <v>132087861</v>
       </c>
       <c r="B21" t="n">
-        <v>87155</v>
+        <v>87161</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2723,7 +2723,7 @@
         <v>132087856</v>
       </c>
       <c r="B22" t="n">
-        <v>87155</v>
+        <v>87161</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2832,7 +2832,7 @@
         <v>132087872</v>
       </c>
       <c r="B23" t="n">
-        <v>87131</v>
+        <v>87137</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2933,7 +2933,7 @@
         <v>132087922</v>
       </c>
       <c r="B24" t="n">
-        <v>91418</v>
+        <v>91424</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 30484-2025 artfynd.xlsx
+++ b/artfynd/A 30484-2025 artfynd.xlsx
@@ -2614,7 +2614,7 @@
         <v>132087861</v>
       </c>
       <c r="B21" t="n">
-        <v>87161</v>
+        <v>87169</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2723,7 +2723,7 @@
         <v>132087856</v>
       </c>
       <c r="B22" t="n">
-        <v>87161</v>
+        <v>87169</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2832,7 +2832,7 @@
         <v>132087872</v>
       </c>
       <c r="B23" t="n">
-        <v>87137</v>
+        <v>87145</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2933,7 +2933,7 @@
         <v>132087922</v>
       </c>
       <c r="B24" t="n">
-        <v>91424</v>
+        <v>91434</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 30484-2025 artfynd.xlsx
+++ b/artfynd/A 30484-2025 artfynd.xlsx
@@ -2614,7 +2614,7 @@
         <v>132087861</v>
       </c>
       <c r="B21" t="n">
-        <v>87169</v>
+        <v>87170</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2723,7 +2723,7 @@
         <v>132087856</v>
       </c>
       <c r="B22" t="n">
-        <v>87169</v>
+        <v>87170</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2832,7 +2832,7 @@
         <v>132087872</v>
       </c>
       <c r="B23" t="n">
-        <v>87145</v>
+        <v>87146</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2933,7 +2933,7 @@
         <v>132087922</v>
       </c>
       <c r="B24" t="n">
-        <v>91434</v>
+        <v>91435</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 30484-2025 artfynd.xlsx
+++ b/artfynd/A 30484-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY24"/>
+  <dimension ref="A1:AY76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,32 +675,27 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>67980013</v>
+        <v>113529619</v>
       </c>
       <c r="B2" t="n">
-        <v>98431</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107708</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222771</v>
+        <v>245</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Skogsklocka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Campanula cervicaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -708,26 +703,17 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Flät, Upl</t>
+          <t>Gävle_Älvkarleby, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>629929.9683871801</v>
+        <v>629897</v>
       </c>
       <c r="R2" t="n">
-        <v>6720253.867080142</v>
+        <v>6720290</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,27 +740,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2017-06-02</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-10-01</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2017-06-02</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-10-01</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>spridda i örtbarrskog 80-100 år</t>
+          <t>Calluna_AB</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -789,27 +765,26 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Tommy Löfgren</t>
+          <t>Tom Brodin</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Tommy Löfgren</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr"/>
+          <t>Tom Brodin, Milad Avalinejad Bandari</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>AKE0012 Kompletterande NVI del 2</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>67980122</v>
+        <v>113529621</v>
       </c>
       <c r="B3" t="n">
-        <v>106707</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107708</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -817,16 +792,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220204</v>
+        <v>245</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Slåtterfibbla</t>
+          <t>Skogsklocka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hypochaeris maculata</t>
+          <t>Campanula cervicaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -834,26 +809,17 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Flät, Upl</t>
+          <t>Gävle_Älvkarleby, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>629878.8893549375</v>
+        <v>629853</v>
       </c>
       <c r="R3" t="n">
-        <v>6720263.822656532</v>
+        <v>6720269</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -880,22 +846,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2017-06-02</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-10-01</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2017-06-02</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-10-01</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Calluna_AB</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -910,67 +871,60 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Tommy Löfgren</t>
+          <t>Tom Brodin</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Tommy Löfgren</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
+          <t>Tom Brodin, Milad Avalinejad Bandari</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>AKE0012 Kompletterande NVI del 2</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>100685592</v>
+        <v>128936491</v>
       </c>
       <c r="B4" t="n">
-        <v>103178</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87403</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221141</v>
+        <v>433</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Duvspindling</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Primula veris</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
+          <t>Cortinarius caesiocanescens s.lat.</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Långgatan, Älvkarleby, Upl</t>
+          <t>Flät, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>629807.2854375856</v>
+        <v>629932</v>
       </c>
       <c r="R4" t="n">
-        <v>6720310.401803494</v>
+        <v>6720234</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -994,22 +948,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2022-05-10</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2022-05-10</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1024,22 +968,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Magnus Stenmark</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Magnus Stenmark</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128481937</v>
+        <v>128952903</v>
       </c>
       <c r="B5" t="n">
-        <v>91061</v>
+        <v>87238</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1047,34 +991,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5747</v>
+        <v>445</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Kopparspindling</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Cortinarius cupreorufus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Flät, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>629885</v>
+        <v>629919</v>
       </c>
       <c r="R5" t="n">
-        <v>6720262</v>
+        <v>6720276</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1101,12 +1048,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1115,6 +1062,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1133,32 +1081,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128494722</v>
+        <v>128952919</v>
       </c>
       <c r="B6" t="n">
-        <v>92831</v>
+        <v>87289</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4366</v>
+        <v>473</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Äggspindling</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Cortinarius meinhardii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>Bon</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1171,10 +1119,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>629919</v>
+        <v>629934</v>
       </c>
       <c r="R6" t="n">
-        <v>6720276</v>
+        <v>6720275</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1201,12 +1149,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1234,48 +1182,54 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128494750</v>
+        <v>104729483</v>
       </c>
       <c r="B7" t="n">
-        <v>86981</v>
+        <v>99024</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6003295</v>
+        <v>504</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Flät, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>629940</v>
+        <v>629850</v>
       </c>
       <c r="R7" t="n">
-        <v>6720267</v>
+        <v>6720260</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1302,12 +1256,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2022-06-09</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2022-06-09</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>11 blommor</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1316,70 +1275,68 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Tommy Löfgren</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Tommy Löfgren</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128494710</v>
+        <v>96059831</v>
       </c>
       <c r="B8" t="n">
-        <v>86944</v>
+        <v>111377</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>3674</v>
+        <v>1242</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Stor bockrot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Pimpinella major</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(L.) Huds.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Flät, Upl</t>
+          <t>Älvkarleby, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>629987</v>
+        <v>629842</v>
       </c>
       <c r="R8" t="n">
-        <v>6720190</v>
+        <v>6720243</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1403,12 +1360,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2021-09-12</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2021-09-12</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1417,70 +1374,80 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Magnus Stenmark</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Magnus Stenmark</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128482901</v>
+        <v>102538795</v>
       </c>
       <c r="B9" t="n">
-        <v>86958</v>
+        <v>111377</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>249228</v>
+        <v>1242</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Barrfagerspindling</t>
+          <t>Stor bockrot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cortinarius piceae</t>
+          <t>Pimpinella major</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Frøslev &amp; al.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
+          <t>(L.) Huds.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Flät, Upl</t>
+          <t>Långgatan, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>629986</v>
+        <v>629902</v>
       </c>
       <c r="R9" t="n">
-        <v>6720246</v>
+        <v>6720279</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1504,12 +1471,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2022-07-20</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2022-07-20</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1518,67 +1485,85 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Vägkant</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Sebastian Sundberg</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Sebastian Sundberg</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128482529</v>
+        <v>102538796</v>
       </c>
       <c r="B10" t="n">
-        <v>86782</v>
+        <v>111377</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>3762</v>
+        <v>1242</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Stor bockrot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Pimpinella major</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(L.) Huds.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Flät, Upl</t>
+          <t>Långgatan, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>629954</v>
+        <v>629878</v>
       </c>
       <c r="R10" t="n">
-        <v>6720288</v>
+        <v>6720270</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1602,12 +1587,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2022-07-20</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2022-07-20</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1618,64 +1603,66 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Vägkant</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Sebastian Sundberg</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Sebastian Sundberg</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128494737</v>
+        <v>113529590</v>
       </c>
       <c r="B11" t="n">
-        <v>86782</v>
+        <v>111377</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>3762</v>
+        <v>1242</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Stor bockrot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Pimpinella major</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>(L.) Huds.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Flät, Upl</t>
+          <t>Gävle_Älvkarleby, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>629913</v>
+        <v>629844</v>
       </c>
       <c r="R11" t="n">
-        <v>6720256</v>
+        <v>6720243</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1702,12 +1689,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2022-10-01</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2022-10-01</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Calluna_AB</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1716,55 +1708,70 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Tom Brodin</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr"/>
+          <t>Tom Brodin, Milad Avalinejad Bandari</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>AKE0012 Kompletterande NVI del 2</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128481990</v>
+        <v>128494710</v>
       </c>
       <c r="B12" t="n">
-        <v>92848</v>
+        <v>87309</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5449</v>
+        <v>3674</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Anisspindling</t>
+        </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr"/>
+          <t>Cortinarius odorifer</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Britzelm.</t>
+        </is>
+      </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Flät, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>629885</v>
+        <v>629987</v>
       </c>
       <c r="R12" t="n">
-        <v>6720262</v>
+        <v>6720190</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1805,6 +1812,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1823,10 +1831,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128482768</v>
+        <v>132087856</v>
       </c>
       <c r="B13" t="n">
-        <v>86994</v>
+        <v>87232</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1834,25 +1842,33 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6003295</v>
+        <v>3712</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
@@ -1861,10 +1877,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>629958</v>
+        <v>629950</v>
       </c>
       <c r="R13" t="n">
-        <v>6720276</v>
+        <v>6720280</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1924,32 +1940,44 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128885154</v>
+        <v>132087861</v>
       </c>
       <c r="B14" t="n">
-        <v>92839</v>
+        <v>87232</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6047725</v>
+        <v>3712</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rödfläckig zontaggsvamp</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum rufoconcrescens nom.prov.</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
+          <t>Cortinarius salor</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
@@ -1958,10 +1986,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>629954</v>
+        <v>629975</v>
       </c>
       <c r="R14" t="n">
-        <v>6720288</v>
+        <v>6720276</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2021,10 +2049,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128952919</v>
+        <v>128935482</v>
       </c>
       <c r="B15" t="n">
-        <v>86948</v>
+        <v>87375</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2032,37 +2060,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>473</v>
+        <v>3739</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Äggspindling</t>
+          <t>Persiljespindling</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cortinarius meinhardii</t>
+          <t>Cortinarius sulfurinus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Bon</t>
+          <t>Quél.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Flät, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>629934</v>
+        <v>629912</v>
       </c>
       <c r="R15" t="n">
-        <v>6720275</v>
+        <v>6720245</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2103,7 +2128,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2122,48 +2146,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128952903</v>
+        <v>128482529</v>
       </c>
       <c r="B16" t="n">
-        <v>86897</v>
+        <v>87146</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>445</v>
+        <v>3762</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kopparspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cortinarius cupreorufus</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Flät, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>629919</v>
+        <v>629954</v>
       </c>
       <c r="R16" t="n">
-        <v>6720276</v>
+        <v>6720288</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2190,12 +2211,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2204,7 +2225,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2223,45 +2243,48 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128936574</v>
+        <v>128494737</v>
       </c>
       <c r="B17" t="n">
-        <v>92327</v>
+        <v>87146</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>232138</v>
+        <v>3762</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gul lammticka</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Albatrellus citrinus</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Ryman</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Flät, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>629919</v>
+        <v>629913</v>
       </c>
       <c r="R17" t="n">
-        <v>6720276</v>
+        <v>6720256</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2288,12 +2311,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2302,6 +2325,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2320,45 +2344,48 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128935482</v>
+        <v>132087872</v>
       </c>
       <c r="B18" t="n">
-        <v>87034</v>
+        <v>87208</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>3739</v>
+        <v>3762</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Persiljespindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cortinarius sulfurinus</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Quél.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Flät, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>629912</v>
+        <v>629978</v>
       </c>
       <c r="R18" t="n">
-        <v>6720245</v>
+        <v>6720214</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2385,12 +2412,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2399,6 +2426,7 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2417,10 +2445,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128953115</v>
+        <v>128494722</v>
       </c>
       <c r="B19" t="n">
-        <v>87005</v>
+        <v>93209</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2428,21 +2456,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6003295</v>
+        <v>4366</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2485,12 +2513,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2518,44 +2546,49 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128936491</v>
+        <v>96059856</v>
       </c>
       <c r="B20" t="n">
-        <v>87062</v>
+        <v>89081</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>433</v>
+        <v>4374</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Duvspindling</t>
+          <t>Gulvaxing</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Cortinarius caesiocanescens s.lat.</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr"/>
+          <t>Hygrocybe chlorophana</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Fr.) Wünsche</t>
+        </is>
+      </c>
       <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Flät, Upl</t>
+          <t>Älvkarleby, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>629932</v>
+        <v>629844</v>
       </c>
       <c r="R20" t="n">
         <v>6720234</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2579,12 +2612,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2021-09-12</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2021-09-12</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2599,68 +2632,57 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Magnus Stenmark</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Magnus Stenmark</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132087861</v>
+        <v>128481937</v>
       </c>
       <c r="B21" t="n">
-        <v>87173</v>
+        <v>91435</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>3712</v>
+        <v>5747</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Fr.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
+          <t>Christan</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Flät, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>629975</v>
+        <v>629885</v>
       </c>
       <c r="R21" t="n">
-        <v>6720276</v>
+        <v>6720262</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2701,7 +2723,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2720,37 +2741,37 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>132087856</v>
+        <v>132087922</v>
       </c>
       <c r="B22" t="n">
-        <v>87173</v>
+        <v>91500</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>3712</v>
+        <v>5747</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -2766,10 +2787,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>629950</v>
+        <v>629915</v>
       </c>
       <c r="R22" t="n">
-        <v>6720280</v>
+        <v>6720225</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2829,10 +2850,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>132087872</v>
+        <v>96059827</v>
       </c>
       <c r="B23" t="n">
-        <v>87149</v>
+        <v>57945</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2840,40 +2861,48 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>3762</v>
+        <v>100110</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Gråspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Picus canus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
+          <t>J.F. Gmelin, 1788</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Flät, Upl</t>
+          <t>Älvkarleby, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>629978</v>
+        <v>629868</v>
       </c>
       <c r="R23" t="n">
-        <v>6720214</v>
+        <v>6720245</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2897,12 +2926,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2021-09-12</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2021-09-12</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2911,75 +2940,63 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Magnus Stenmark</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Magnus Stenmark</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>132087922</v>
+        <v>63558541</v>
       </c>
       <c r="B24" t="n">
-        <v>91438</v>
+        <v>43438</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5747</v>
+        <v>101298</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Sotnätfjäril</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Melitaea diamina</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Christan</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
+          <t>(Lang, 1789)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Flät, Upl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>629915</v>
+        <v>629865</v>
       </c>
       <c r="R24" t="n">
-        <v>6720225</v>
+        <v>6720204</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3006,12 +3023,17 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>1999-01-01</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>1999-01-01</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>10 meter, Flät 2b, Källa: I Frycklund, 2001, kraftledning</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3020,22 +3042,5601 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
+          <t>Per Stolpe</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Ingemar Frycklund</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>63558542</v>
+      </c>
+      <c r="B25" t="n">
+        <v>42214</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>101774</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Större borstspinnare</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Setina irrorella</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Flät, Upl</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>629865</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6720204</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>1999-01-01</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>1999-01-01</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>10 meter, Flät 2b, Källa: I Frycklund, 2001, kraftledning</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Per Stolpe</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Ingemar Frycklund</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>15752277</v>
+      </c>
+      <c r="B26" t="n">
+        <v>45044</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>102018</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Bredbrämad bastardsvärmare</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Zygaena lonicerae</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Scheven, 1777)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Flät, kraftledningsgatan, Upl</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>629834</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6720248</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2013-07-15</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2013-07-15</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>1 ex</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>Gräsmark på kalkrikt underlag</t>
+        </is>
+      </c>
+      <c r="AR26" t="inlineStr"/>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Lars-Thure Nordin</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Oskar Löfgren</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>75660926</v>
+      </c>
+      <c r="B27" t="n">
+        <v>45046</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>102020</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Smalsprötad bastardsvärmare</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Zygaena osterodensis</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Reiss, 1921</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Flät 6 km NV om Älvkarleby, Upl</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>629896</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6720180</v>
+      </c>
+      <c r="S27" t="n">
+        <v>25</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2002-07-02</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2002-07-02</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>1 imago på åkervädd (Knautia arvensis).</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>Äldre, örtrik kraftledningsgata.</t>
+        </is>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>15752302</v>
+      </c>
+      <c r="B28" t="n">
+        <v>45049</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>102021</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Mindre bastardsvärmare</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Zygaena viciae</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Flät, kraftledningsgatan, Upl</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>629796</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6720272</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2013-07-15</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2013-07-15</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>1 ex</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>Gräsmark på kalkrikt underlag</t>
+        </is>
+      </c>
+      <c r="AR28" t="inlineStr"/>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Lars-Thure Nordin</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Oskar Löfgren</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>63216569</v>
+      </c>
+      <c r="B29" t="n">
+        <v>45049</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>102021</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Mindre bastardsvärmare</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Zygaena viciae</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Flät, Upl</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>629865</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6720204</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2000-01-01</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2000-01-01</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Flät 2b</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AR29" t="inlineStr"/>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Per Stolpe</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Pär Eriksson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>63558536</v>
+      </c>
+      <c r="B30" t="n">
+        <v>40642</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>102372</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Fyrpunktsplattmal/mindre säfferotsplattmal</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Agonopterix quadripunctata s.lat.</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Flät, Upl</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>629865</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6720204</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>1999-01-01</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>1999-01-01</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>10 meter, Flät 2b, Källa: I Frycklund, 2001, kraftledning</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Per Stolpe</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Ingemar Frycklund</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>63558539</v>
+      </c>
+      <c r="B31" t="n">
+        <v>40693</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>102453</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Jungfrulinspraktmal</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Hypercallia citrinalis</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Flät, Upl</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>629865</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6720204</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>1999-01-01</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>1999-01-01</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>10 meter, Flät 2b, Källa: I Frycklund, 2001, kraftledning</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Per Stolpe</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Ingemar Frycklund</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>75953596</v>
+      </c>
+      <c r="B32" t="n">
+        <v>43285</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>201143</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Ängsblåvinge</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Cyaniris semiargus</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Rottemburg, 1775)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Flät 6 km NV om Älvkarleby, Upl</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>629837</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6720243</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2004-06-21</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2004-06-21</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>3 hanar.</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI32" t="inlineStr">
+        <is>
+          <t>Äldre kraftledningsgata.</t>
+        </is>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>75953597</v>
+      </c>
+      <c r="B33" t="n">
+        <v>43285</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>201143</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Ängsblåvinge</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Cyaniris semiargus</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Rottemburg, 1775)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Flät 6 km NV om Älvkarleby, Upl</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>629898</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6720183</v>
+      </c>
+      <c r="S33" t="n">
+        <v>25</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2002-07-02</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2002-07-02</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>1 hona.</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI33" t="inlineStr">
+        <is>
+          <t>Äldre kraftledningsgata.</t>
+        </is>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>81679745</v>
+      </c>
+      <c r="B34" t="n">
+        <v>45042</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>201164</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Sexfläckig bastardsvärmare</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Zygaena filipendulae</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Flät, Upl</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>629824</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6720252</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2019-07-08</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2019-07-08</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Tommy Löfgren</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Tommy Löfgren</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>63558535</v>
+      </c>
+      <c r="B35" t="n">
+        <v>40657</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>214286</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Ljusryggad bockrotsplattmal</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Depressaria pulcherrimella</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Stainton, 1849</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Flät, Upl</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>629865</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6720204</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>1999-01-01</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>1999-01-01</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>10 meter, Flät 2b, Källa: I Frycklund, 2001, kraftledning</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Per Stolpe</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Ingemar Frycklund</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>63558532</v>
+      </c>
+      <c r="B36" t="n">
+        <v>40966</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>214735</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Rödblärearvmal</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Caryocolum viscariellum</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Stainton, 1855)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Flät, Upl</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>629865</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6720204</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2000-01-01</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2000-01-01</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>10 meter, Flät 2b, Källa: I Frycklund, 2001, kraftledning</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Per Stolpe</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Ingemar Frycklund</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>63558544</v>
+      </c>
+      <c r="B37" t="n">
+        <v>42274</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>215930</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Jungfrulinsfly</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Phytometra viridaria</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Clerck, 1759)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Flät, Upl</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>629865</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6720204</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>1999-01-01</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>1999-01-01</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>10 meter, Flät 2b, Källa: I Frycklund, 2001, kraftledning</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Per Stolpe</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Ingemar Frycklund</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>7187692</v>
+      </c>
+      <c r="B38" t="n">
+        <v>111405</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>219719</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Säfferot</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Seseli libanotis</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(L.) W. D. J. Koch</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Flät, kraftledningsgatan, Upl</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>629850</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6720239</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2013-07-03</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2013-07-03</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>1000-tals ex, 3/7 13</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS38" t="inlineStr">
+        <is>
+          <t>Tommy Löfgren</t>
+        </is>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Lars-Thure Nordin</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Lars-Thure Nordin</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>60251390</v>
+      </c>
+      <c r="B39" t="n">
+        <v>111405</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>219719</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Säfferot</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Seseli libanotis</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(L.) W. D. J. Koch</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Flät, Kraftledningsgata, Upl</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>629850</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6720263</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2016-06-22</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2016-06-22</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Göran Frisk</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Kristina Nygren Frisk, Göran Frisk</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>94061273</v>
+      </c>
+      <c r="B40" t="n">
+        <v>111405</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>219719</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Säfferot</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Seseli libanotis</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(L.) W. D. J. Koch</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Flät, Upl</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>629880</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6720217</v>
+      </c>
+      <c r="S40" t="n">
+        <v>5</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2021-06-04</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2021-06-04</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF40" t="inlineStr"/>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Göran Frisk</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Göran Frisk</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>96059833</v>
+      </c>
+      <c r="B41" t="n">
+        <v>111405</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>219719</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Säfferot</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Seseli libanotis</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(L.) W. D. J. Koch</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Älvkarleby, Upl</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>629842</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6720243</v>
+      </c>
+      <c r="S41" t="n">
+        <v>25</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2021-09-12</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2021-09-12</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Magnus Stenmark</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Magnus Stenmark</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>102538797</v>
+      </c>
+      <c r="B42" t="n">
+        <v>111405</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>219719</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Säfferot</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Seseli libanotis</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(L.) W. D. J. Koch</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Flät, kraftledningsgatan, Upl</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>629849</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6720227</v>
+      </c>
+      <c r="S42" t="n">
+        <v>5</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2022-07-20</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2022-07-20</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Endast blommande plantor räknade inom en yta av ca 75 x 50 m, sterila bladrosetter ej medräknade</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF42" t="inlineStr"/>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH42" t="inlineStr">
+        <is>
+          <t>Frisk gräsmark</t>
+        </is>
+      </c>
+      <c r="AI42" t="inlineStr">
+        <is>
+          <t>Kraftledningsgata</t>
+        </is>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Sebastian Sundberg</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Sebastian Sundberg</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>113529593</v>
+      </c>
+      <c r="B43" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Gävle_Älvkarleby, Upl</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>629838</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6720254</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2022-10-01</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2022-10-01</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Calluna_AB</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Tom Brodin</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Tom Brodin, Milad Avalinejad Bandari</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr">
+        <is>
+          <t>AKE0012 Kompletterande NVI del 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>113529591</v>
+      </c>
+      <c r="B44" t="n">
+        <v>99096</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Gävle_Älvkarleby, Upl</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>629890</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6720281</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2022-10-01</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2022-10-01</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Calluna_AB</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Tom Brodin</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Tom Brodin, Milad Avalinejad Bandari</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr">
+        <is>
+          <t>AKE0012 Kompletterande NVI del 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>113529620</v>
+      </c>
+      <c r="B45" t="n">
+        <v>99096</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Gävle_Älvkarleby, Upl</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>629896</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6720292</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2022-10-01</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2022-10-01</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Calluna_AB</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Tom Brodin</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Tom Brodin, Milad Avalinejad Bandari</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr">
+        <is>
+          <t>AKE0012 Kompletterande NVI del 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>113529626</v>
+      </c>
+      <c r="B46" t="n">
+        <v>99096</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Gävle_Älvkarleby, Upl</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>629888</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6720273</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2022-10-01</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2022-10-01</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Calluna_AB</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Tom Brodin</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Tom Brodin, Milad Avalinejad Bandari</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr">
+        <is>
+          <t>AKE0012 Kompletterande NVI del 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>113529699</v>
+      </c>
+      <c r="B47" t="n">
+        <v>99096</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Gävle_Älvkarleby, Upl</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>629827</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6720240</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2022-10-01</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2022-10-01</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Calluna_AB</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Tom Brodin</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Tom Brodin, Milad Avalinejad Bandari</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr">
+        <is>
+          <t>AKE0012 Kompletterande NVI del 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>7187690</v>
+      </c>
+      <c r="B48" t="n">
+        <v>99120</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>219811</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Brudsporre</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Gymnadenia conopsea</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Flät, kraftledningsgatan, Upl</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>629827</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6720239</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2013-07-03</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2013-07-03</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>300 ex</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS48" t="inlineStr">
+        <is>
+          <t>Tommy Löfgren</t>
+        </is>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Lars-Thure Nordin</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Lars-Thure Nordin</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>61999743</v>
+      </c>
+      <c r="B49" t="n">
+        <v>99120</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>219811</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Brudsporre</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Gymnadenia conopsea</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Flät, kraftledningsgatan, Upl</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>629827</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6720238</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2013-07-03</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2013-07-03</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Tommy Löfgren</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Tommy Löfgren</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>113529700</v>
+      </c>
+      <c r="B50" t="n">
+        <v>99120</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>219811</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Brudsporre</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Gymnadenia conopsea</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Gävle_Älvkarleby, Upl</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>629839</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6720247</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2022-10-01</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2022-10-01</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Calluna_AB</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Tom Brodin</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Tom Brodin, Milad Avalinejad Bandari</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr">
+        <is>
+          <t>AKE0012 Kompletterande NVI del 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>7187667</v>
+      </c>
+      <c r="B51" t="n">
+        <v>108194</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>220103</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Klasefibbla</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Crepis praemorsa</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(L.) Walther</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Flät, kraftledningsgatan, Upl</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>629795</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6720282</v>
+      </c>
+      <c r="S51" t="n">
+        <v>10</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2013-07-03</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2013-07-03</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>4 kvm, spridd i artrika ängen</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS51" t="inlineStr">
+        <is>
+          <t>Tommy Löfgren</t>
+        </is>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Lars-Thure Nordin</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Lars-Thure Nordin</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>62000259</v>
+      </c>
+      <c r="B52" t="n">
+        <v>108194</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>220103</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Klasefibbla</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Crepis praemorsa</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(L.) Walther</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Flät, kraftledningsgatan, Upl</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>629795</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6720283</v>
+      </c>
+      <c r="S52" t="n">
+        <v>10</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2013-07-03</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2013-07-03</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>spridd i artrika ängen</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Tommy Löfgren</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Tommy Löfgren</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>96059839</v>
+      </c>
+      <c r="B53" t="n">
+        <v>108194</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>220103</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Klasefibbla</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Crepis praemorsa</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(L.) Walther</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Älvkarleby, Upl</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>629835</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6720259</v>
+      </c>
+      <c r="S53" t="n">
+        <v>25</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2021-09-12</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2021-09-12</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Magnus Stenmark</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Magnus Stenmark</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>104729444</v>
+      </c>
+      <c r="B54" t="n">
+        <v>108194</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>220103</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Klasefibbla</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Crepis praemorsa</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(L.) Walther</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Flät, Upl</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>629833</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6720262</v>
+      </c>
+      <c r="S54" t="n">
+        <v>10</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2022-06-09</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2022-06-09</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Tommy Löfgren</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Tommy Löfgren</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>129107975</v>
+      </c>
+      <c r="B55" t="n">
+        <v>108193</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>220103</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Klasefibbla</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Crepis praemorsa</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(L.) Walther</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Skutskär - Mehedeby, Upl</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>629867</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6720209</v>
+      </c>
+      <c r="S55" t="n">
+        <v>10</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Alexandra Östberg</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Benny Willman</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>67980122</v>
+      </c>
+      <c r="B56" t="n">
+        <v>109815</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>220204</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Slåtterfibbla</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Hypochaeris maculata</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Flät, Upl</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>629879</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6720264</v>
+      </c>
+      <c r="S56" t="n">
+        <v>10</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2017-06-02</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2017-06-02</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Tommy Löfgren</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Tommy Löfgren</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>113529623</v>
+      </c>
+      <c r="B57" t="n">
+        <v>109815</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>220204</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Slåtterfibbla</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Hypochaeris maculata</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Gävle_Älvkarleby, Upl</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>629849</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6720239</v>
+      </c>
+      <c r="S57" t="n">
+        <v>10</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2022-10-01</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2022-10-01</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Calluna_AB</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Tom Brodin</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Tom Brodin, Milad Avalinejad Bandari</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr">
+        <is>
+          <t>AKE0012 Kompletterande NVI del 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>57458421</v>
+      </c>
+      <c r="B58" t="n">
+        <v>106140</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>221137</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Majviva</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Primula farinosa</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Kraftledningsgata Norr Turkiet 4, Upl</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>629977</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6720120</v>
+      </c>
+      <c r="S58" t="n">
+        <v>10</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2015-06-04</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2015-06-04</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Bengt Hemström</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Bengt Hemström</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>100685592</v>
+      </c>
+      <c r="B59" t="n">
+        <v>106156</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>221141</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Gullviva</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Primula veris</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Långgatan, Älvkarleby, Upl</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>629807</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6720311</v>
+      </c>
+      <c r="S59" t="n">
+        <v>25</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2022-05-10</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2022-05-10</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Magnus Stenmark</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Magnus Stenmark</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>110886999</v>
+      </c>
+      <c r="B60" t="n">
+        <v>106156</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>221141</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Gullviva</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Primula veris</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Västanån, Upl</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>629904</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6720281</v>
+      </c>
+      <c r="S60" t="n">
+        <v>10</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2023-06-20</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2023-06-20</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Johanna Kühne</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Johanna Kühne</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>110887001</v>
+      </c>
+      <c r="B61" t="n">
+        <v>106156</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>221141</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Gullviva</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Primula veris</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Västanån, Upl</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>629878</v>
+      </c>
+      <c r="R61" t="n">
+        <v>6720271</v>
+      </c>
+      <c r="S61" t="n">
+        <v>10</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2023-06-20</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2023-06-20</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Johanna Kühne</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Johanna Kühne</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>110886998</v>
+      </c>
+      <c r="B62" t="n">
+        <v>102241</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>221235</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Vårärt</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Lathyrus vernus</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Västanån, Upl</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>629906</v>
+      </c>
+      <c r="R62" t="n">
+        <v>6720285</v>
+      </c>
+      <c r="S62" t="n">
+        <v>10</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2023-06-20</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2023-06-20</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Johanna Kühne</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Johanna Kühne</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>7187693</v>
+      </c>
+      <c r="B63" t="n">
+        <v>102443</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>221333</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Backklöver</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Trifolium montanum</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Flät, kraftledningsgatan, Upl</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>629825</v>
+      </c>
+      <c r="R63" t="n">
+        <v>6720241</v>
+      </c>
+      <c r="S63" t="n">
+        <v>10</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2013-07-03</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2013-07-03</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>10 ex, 3/7 13</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS63" t="inlineStr">
+        <is>
+          <t>Tommy Löfgren</t>
+        </is>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Lars-Thure Nordin</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Lars-Thure Nordin</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>61999699</v>
+      </c>
+      <c r="B64" t="n">
+        <v>102443</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>221333</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Backklöver</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Trifolium montanum</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Flät, kraftledningsgatan, Upl</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>629825</v>
+      </c>
+      <c r="R64" t="n">
+        <v>6720240</v>
+      </c>
+      <c r="S64" t="n">
+        <v>10</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2013-07-03</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2013-07-03</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Tommy Löfgren</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Tommy Löfgren</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>121124890</v>
+      </c>
+      <c r="B65" t="n">
+        <v>102443</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>221333</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Backklöver</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Trifolium montanum</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Flät, Upl</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>629860</v>
+      </c>
+      <c r="R65" t="n">
+        <v>6720258</v>
+      </c>
+      <c r="S65" t="n">
+        <v>10</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2024-06-18</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2024-06-18</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>i vägkant</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Tommy Löfgren</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Tommy Löfgren</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>121124891</v>
+      </c>
+      <c r="B66" t="n">
+        <v>102443</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>221333</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Backklöver</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Trifolium montanum</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Flät, Upl</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>629828</v>
+      </c>
+      <c r="R66" t="n">
+        <v>6720242</v>
+      </c>
+      <c r="S66" t="n">
+        <v>10</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2024-06-18</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2024-06-18</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>i vägkant</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Tommy Löfgren</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Tommy Löfgren</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>110886997</v>
+      </c>
+      <c r="B67" t="n">
+        <v>103683</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>222002</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Underviol</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Viola mirabilis</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Västanån, Upl</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>629918</v>
+      </c>
+      <c r="R67" t="n">
+        <v>6720297</v>
+      </c>
+      <c r="S67" t="n">
+        <v>10</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2023-06-20</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2023-06-20</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Johanna Kühne</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Johanna Kühne</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>110887010</v>
+      </c>
+      <c r="B68" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Västanån, Upl</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>629933</v>
+      </c>
+      <c r="R68" t="n">
+        <v>6720310</v>
+      </c>
+      <c r="S68" t="n">
+        <v>10</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2023-06-20</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2023-06-20</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Lokal direkt i vägkant</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Johanna Kühne</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Johanna Kühne</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>67980013</v>
+      </c>
+      <c r="B69" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Flät, Upl</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>629930</v>
+      </c>
+      <c r="R69" t="n">
+        <v>6720254</v>
+      </c>
+      <c r="S69" t="n">
+        <v>10</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2017-06-02</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2017-06-02</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>spridda i örtbarrskog 80-100 år</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Tommy Löfgren</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Tommy Löfgren</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>110887009</v>
+      </c>
+      <c r="B70" t="n">
+        <v>103403</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>223246</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Skogsalm</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Ulmus glabra</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Huds.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Västanån, Upl</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>629972</v>
+      </c>
+      <c r="R70" t="n">
+        <v>6720327</v>
+      </c>
+      <c r="S70" t="n">
+        <v>10</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2023-06-20</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2023-06-20</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Direkt i vägkant, mindre Skogsalm med föryngring</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Johanna Kühne</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Johanna Kühne</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>128936574</v>
+      </c>
+      <c r="B71" t="n">
+        <v>92688</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>232138</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Gul lammticka</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Albatrellus citrinus</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Ryman</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Flät, Upl</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>629919</v>
+      </c>
+      <c r="R71" t="n">
+        <v>6720276</v>
+      </c>
+      <c r="S71" t="n">
+        <v>10</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
           <t>Anton Björk</t>
         </is>
       </c>
-      <c r="AX24" t="inlineStr">
+      <c r="AX71" t="inlineStr">
         <is>
           <t>Anton Björk</t>
         </is>
       </c>
-      <c r="AY24" t="inlineStr"/>
+      <c r="AY71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>128482901</v>
+      </c>
+      <c r="B72" t="n">
+        <v>87323</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>249228</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Barrfagerspindling</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Cortinarius piceae</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Frøslev &amp; al.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+      <c r="N72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Flät, Upl</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>629986</v>
+      </c>
+      <c r="R72" t="n">
+        <v>6720246</v>
+      </c>
+      <c r="S72" t="n">
+        <v>10</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF72" t="inlineStr"/>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>128482768</v>
+      </c>
+      <c r="B73" t="n">
+        <v>87346</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
+      <c r="N73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Flät, Upl</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>629958</v>
+      </c>
+      <c r="R73" t="n">
+        <v>6720276</v>
+      </c>
+      <c r="S73" t="n">
+        <v>10</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF73" t="inlineStr"/>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>128494750</v>
+      </c>
+      <c r="B74" t="n">
+        <v>87346</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="J74" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
+      <c r="N74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Flät, Upl</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>629940</v>
+      </c>
+      <c r="R74" t="n">
+        <v>6720267</v>
+      </c>
+      <c r="S74" t="n">
+        <v>10</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF74" t="inlineStr"/>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>128953115</v>
+      </c>
+      <c r="B75" t="n">
+        <v>87346</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="J75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
+      <c r="N75" t="inlineStr"/>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Flät, Upl</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>629919</v>
+      </c>
+      <c r="R75" t="n">
+        <v>6720276</v>
+      </c>
+      <c r="S75" t="n">
+        <v>10</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="inlineStr"/>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>128885154</v>
+      </c>
+      <c r="B76" t="n">
+        <v>93211</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>6047725</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Rödfläckig zontaggsvamp</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Hydnellum rufoconcrescens nom.prov.</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr"/>
+      <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr"/>
+      <c r="K76" t="inlineStr"/>
+      <c r="N76" t="inlineStr"/>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Flät, Upl</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>629954</v>
+      </c>
+      <c r="R76" t="n">
+        <v>6720288</v>
+      </c>
+      <c r="S76" t="n">
+        <v>10</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF76" t="inlineStr"/>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 30484-2025 artfynd.xlsx
+++ b/artfynd/A 30484-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY76"/>
+  <dimension ref="A1:AZ76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
           <t>AKE0012 Kompletterande NVI del 2</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113529619</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
           <t>AKE0012 Kompletterande NVI del 2</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113529621</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -977,6 +992,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128936491</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1078,6 +1098,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128952903</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1179,6 +1204,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128952919</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1290,6 +1320,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104729483</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1389,6 +1424,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96059831</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1505,6 +1545,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102538795</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1621,6 +1666,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102538796</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1725,6 +1775,11 @@
       <c r="AY11" t="inlineStr">
         <is>
           <t>AKE0012 Kompletterande NVI del 2</t>
+        </is>
+      </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113529590</t>
         </is>
       </c>
     </row>
@@ -1828,6 +1883,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128494710</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1937,6 +1997,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132087856</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2046,6 +2111,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132087861</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2143,6 +2213,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128935482</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2240,6 +2315,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128482529</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2341,6 +2421,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128494737</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2442,6 +2527,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132087872</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2543,6 +2633,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128494722</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2641,6 +2736,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96059856</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2738,6 +2838,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128481937</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2847,6 +2952,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132087922</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2955,6 +3065,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96059827</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3057,6 +3172,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/63558541</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3159,6 +3279,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/63558542</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3286,6 +3411,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/15752277</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3412,6 +3542,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75660926</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3539,6 +3674,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/15752302</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3642,6 +3782,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/63216569</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3740,6 +3885,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/63558536</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3842,6 +3992,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/63558539</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3973,6 +4128,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75953596</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4104,6 +4264,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75953597</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4215,6 +4380,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81679745</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4317,6 +4487,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/63558535</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4419,6 +4594,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/63558532</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4521,6 +4701,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/63558544</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4637,6 +4822,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/7187692</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4745,6 +4935,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/60251390</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4851,6 +5046,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94061273</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4950,6 +5150,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96059833</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5079,6 +5284,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102538797</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5185,6 +5395,11 @@
           <t>AKE0012 Kompletterande NVI del 2</t>
         </is>
       </c>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113529593</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5291,6 +5506,11 @@
           <t>AKE0012 Kompletterande NVI del 2</t>
         </is>
       </c>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113529591</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5397,6 +5617,11 @@
           <t>AKE0012 Kompletterande NVI del 2</t>
         </is>
       </c>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113529620</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5503,6 +5728,11 @@
           <t>AKE0012 Kompletterande NVI del 2</t>
         </is>
       </c>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113529626</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5609,6 +5839,11 @@
           <t>AKE0012 Kompletterande NVI del 2</t>
         </is>
       </c>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113529699</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5725,6 +5960,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/7187690</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5831,6 +6071,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61999743</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5937,6 +6182,11 @@
           <t>AKE0012 Kompletterande NVI del 2</t>
         </is>
       </c>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113529700</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6053,6 +6303,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/7187667</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6164,6 +6419,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62000259</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6263,6 +6523,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96059839</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6369,6 +6634,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104729444</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6475,6 +6745,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129107975</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6581,6 +6856,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67980122</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6687,6 +6967,11 @@
           <t>AKE0012 Kompletterande NVI del 2</t>
         </is>
       </c>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113529623</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6793,6 +7078,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/57458421</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6892,6 +7182,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100685592</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6989,6 +7284,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110886999</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7086,6 +7386,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110887001</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7183,6 +7488,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110886998</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7299,6 +7609,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/7187693</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7405,6 +7720,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61999699</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7516,6 +7836,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121124890</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7627,6 +7952,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121124891</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7724,6 +8054,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110886997</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7826,6 +8161,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110887010</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7937,6 +8277,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67980013</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -8039,6 +8384,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110887009</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8136,6 +8486,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128936574</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8237,6 +8592,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128482901</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8338,6 +8698,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128482768</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8439,6 +8804,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128494750</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8540,6 +8910,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128953115</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8637,8 +9012,90 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128885154</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>